--- a/缓存数据/newOdercityCsmAndoldacct.xlsx
+++ b/缓存数据/newOdercityCsmAndoldacct.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9291.73</v>
+        <v>9280.239999999998</v>
       </c>
       <c r="C2" t="n">
-        <v>18973.95</v>
+        <v>12523.33</v>
       </c>
       <c r="D2" t="n">
-        <v>733.97</v>
+        <v>733.49</v>
       </c>
       <c r="E2" t="n">
-        <v>522.15</v>
+        <v>606.0700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9280.239999999998</v>
+        <v>9153.860000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>12523.33</v>
+        <v>18211.78</v>
       </c>
       <c r="D3" t="n">
-        <v>733.4900000000001</v>
+        <v>489.45</v>
       </c>
       <c r="E3" t="n">
-        <v>606.0700000000001</v>
+        <v>480.34</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9153.860000000001</v>
+        <v>12751.43</v>
       </c>
       <c r="C4" t="n">
-        <v>18211.78</v>
+        <v>19574.66</v>
       </c>
       <c r="D4" t="n">
-        <v>489.45</v>
+        <v>240.85</v>
       </c>
       <c r="E4" t="n">
-        <v>480.34</v>
+        <v>492.59</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12751.43</v>
+        <v>10072.7</v>
       </c>
       <c r="C5" t="n">
-        <v>19574.66</v>
+        <v>9374.170000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>240.85</v>
+        <v>57.23</v>
       </c>
       <c r="E5" t="n">
-        <v>492.59</v>
+        <v>359.0300000000001</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10072.7</v>
+        <v>10704.51</v>
       </c>
       <c r="C6" t="n">
-        <v>9374.17</v>
+        <v>9418.82</v>
       </c>
       <c r="D6" t="n">
-        <v>57.23</v>
+        <v>468.6200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>359.03</v>
+        <v>933.3700000000001</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10704.51</v>
+        <v>8662.869999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>9418.82</v>
+        <v>8384.099999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>468.62</v>
+        <v>700.01</v>
       </c>
       <c r="E7" t="n">
-        <v>933.37</v>
+        <v>478.3200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8662.869999999999</v>
+        <v>10418.29</v>
       </c>
       <c r="C8" t="n">
-        <v>8384.099999999999</v>
+        <v>12393.29</v>
       </c>
       <c r="D8" t="n">
-        <v>700.01</v>
+        <v>621.4599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>478.3200000000001</v>
+        <v>754.37</v>
       </c>
     </row>
     <row r="9">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10418.29</v>
+        <v>8898.559999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>12393.29</v>
+        <v>24216.11</v>
       </c>
       <c r="D9" t="n">
-        <v>621.4599999999999</v>
+        <v>749.7399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>754.3700000000001</v>
+        <v>600.73</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/newOdercityCsmAndoldacct.xlsx
+++ b/缓存数据/newOdercityCsmAndoldacct.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9280.239999999998</v>
+        <v>13803.08</v>
       </c>
       <c r="C2" t="n">
-        <v>12523.33</v>
+        <v>51025.31</v>
       </c>
       <c r="D2" t="n">
-        <v>733.49</v>
+        <v>5178.94</v>
       </c>
       <c r="E2" t="n">
-        <v>606.0700000000001</v>
+        <v>334.58</v>
       </c>
     </row>
     <row r="3">
@@ -476,16 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9153.860000000001</v>
+        <v>14390.74</v>
       </c>
       <c r="C3" t="n">
-        <v>18211.78</v>
+        <v>107691.68</v>
       </c>
       <c r="D3" t="n">
-        <v>489.45</v>
+        <v>6089.110000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>480.34</v>
+        <v>657.65</v>
       </c>
     </row>
     <row r="4">
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12751.43</v>
+        <v>22986.25</v>
       </c>
       <c r="C4" t="n">
-        <v>19574.66</v>
+        <v>45430.81999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>240.85</v>
+        <v>8982.77</v>
       </c>
       <c r="E4" t="n">
-        <v>492.59</v>
+        <v>262.42</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10072.7</v>
+        <v>24032.78</v>
       </c>
       <c r="C5" t="n">
-        <v>9374.170000000002</v>
+        <v>43087</v>
       </c>
       <c r="D5" t="n">
-        <v>57.23</v>
+        <v>6011.530000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>359.0300000000001</v>
+        <v>216.75</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10704.51</v>
+        <v>9075.48</v>
       </c>
       <c r="C6" t="n">
-        <v>9418.82</v>
+        <v>48950.43000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>468.6200000000001</v>
+        <v>4189.48</v>
       </c>
       <c r="E6" t="n">
-        <v>933.3700000000001</v>
+        <v>149.02</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8662.869999999999</v>
+        <v>7679.629999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>8384.099999999999</v>
+        <v>47336.26</v>
       </c>
       <c r="D7" t="n">
-        <v>700.01</v>
+        <v>3862.32</v>
       </c>
       <c r="E7" t="n">
-        <v>478.3200000000001</v>
+        <v>143.07</v>
       </c>
     </row>
     <row r="8">
@@ -571,16 +571,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10418.29</v>
+        <v>11306.49</v>
       </c>
       <c r="C8" t="n">
-        <v>12393.29</v>
+        <v>38862.86</v>
       </c>
       <c r="D8" t="n">
-        <v>621.4599999999999</v>
+        <v>5761.28</v>
       </c>
       <c r="E8" t="n">
-        <v>754.37</v>
+        <v>204.15</v>
       </c>
     </row>
     <row r="9">
@@ -590,19 +590,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8898.559999999999</v>
+        <v>10995.12</v>
       </c>
       <c r="C9" t="n">
-        <v>24216.11</v>
+        <v>39989.26</v>
       </c>
       <c r="D9" t="n">
-        <v>749.7399999999999</v>
+        <v>4910.28</v>
       </c>
       <c r="E9" t="n">
-        <v>600.73</v>
+        <v>278.48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>